--- a/public/files/templates/Template_IK.xlsx
+++ b/public/files/templates/Template_IK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Victus\Desktop\Asesmen-CPL\public\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2421F165-E27E-4436-80CC-EA6B1E028C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381658E-A83D-4AED-8C2C-D4C4881029E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50BCFC4E-77CD-4EFE-8DDF-B5E956CC2D9E}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Kode CP</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Kode IK</t>
   </si>
@@ -475,14 +472,14 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="49.6640625" style="4" customWidth="1"/>
-    <col min="4" max="8" width="25.77734375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" style="4" customWidth="1"/>
+    <col min="3" max="7" width="25.77734375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="0" style="2" hidden="1"/>
     <col min="9" max="16384" width="8.88671875" style="2" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,14 +501,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Zg0ebc8b7cJNC5vYbyUbMlIsk88E+NsuVKYvrELGa1uRXZnhBqz7ZdtMaGLQ9Inqp0xRPM0hjmYjCqfydCIxUQ==" saltValue="A+6lRyOFG0bRFjvh02FE1g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/dorQg1FL55NQQHcvWDCX/2fcWZkEEzdf/oQJzA/0zBlp+bOO2ZB/jS2G9XcR6SnxTjEuxzEuAgt/awj7ljc6A==" saltValue="TICaWxG1fdB4wMRjI5qX2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A2:H1048576" name="Range1"/>
+    <protectedRange sqref="A2:G1048576" name="Range1"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
